--- a/output/PRICE_HISTORY.xlsx
+++ b/output/PRICE_HISTORY.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -504,12 +504,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:31.896064+00:00</t>
+          <t>2026-08-06T10:52:12.882440+00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -594,12 +594,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -680,12 +680,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -715,12 +715,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:31.896064+00:00</t>
+          <t>2026-08-06T10:52:12.882440+00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -862,12 +862,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:31.896064+00:00</t>
+          <t>2026-08-06T10:52:12.882440+00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:31.896064+00:00</t>
+          <t>2026-08-06T10:52:12.882440+00:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PRC.xlsx</t>
+          <t>PRC_202412150928-Дистрибьюторская Цена.xlsx</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-05T18:59:32.896064+00:00</t>
+          <t>2026-08-06T10:52:13.882440+00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
